--- a/documentation/f1_dataset_arch.xlsx
+++ b/documentation/f1_dataset_arch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\GitHub\f1_penalty_predictor\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DD22EC-EAE1-4D56-AE4A-4D2F8ECAAA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6FDD88-F3E7-446E-952A-2572D47D8ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DE7B187D-0900-46B5-9C23-74B527DD2856}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DE7B187D-0900-46B5-9C23-74B527DD2856}"/>
   </bookViews>
   <sheets>
     <sheet name="lookable" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="70">
   <si>
     <t>F1 DATASET STRUCTURE</t>
   </si>
@@ -291,10 +291,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,514 +613,514 @@
   <dimension ref="A1:AN6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.44140625" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.44140625" customWidth="1"/>
-    <col min="30" max="30" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="59.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="36.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="11.21875" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.33203125" customWidth="1"/>
-    <col min="39" max="39" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="43.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
       <c r="AN1" s="1"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2" t="s">
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
       <c r="AG2" s="1"/>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
       <c r="AN2" s="1"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3" t="s">
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AI3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AK3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AL3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AM3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN3" s="3"/>
+      <c r="AN3" s="2"/>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>1950</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>14</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>2021</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>22</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>10</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>27</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <f>L4-J4</f>
         <v>26</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>53</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <f>(J4/L4)*100</f>
         <v>50.943396226415096</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <v>2</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="Z4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AA4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AB4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AC4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AD4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AE4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AF4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3" t="b">
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AI4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AJ4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AK4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AL4" s="2">
         <v>2</v>
       </c>
-      <c r="AM4" s="3" t="s">
+      <c r="AM4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AN4" s="3"/>
+      <c r="AN4" s="2"/>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AK6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN6" s="3"/>
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN6" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1138,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EDD3023-539C-4909-99C8-8BF0EE71A5FA}">
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -1183,291 +1183,380 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AA2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AB2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AC2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AE2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AF2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3" t="s">
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AI2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AK2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AL2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AM2" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>1950</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>14</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>2021</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>22</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>10</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>27</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f>L3-J3</f>
         <v>26</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>53</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <f>(J3/L3)*100</f>
         <v>50.943396226415096</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>1</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <v>2</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3" t="b">
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AI3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AK3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AL3" s="3">
+      <c r="AL3" s="2">
         <v>2</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AM3" s="2" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/f1_dataset_arch.xlsx
+++ b/documentation/f1_dataset_arch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\GitHub\f1_penalty_predictor\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6FDD88-F3E7-446E-952A-2572D47D8ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C5E8E-F7D7-4EDA-A88E-7FA7119203FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DE7B187D-0900-46B5-9C23-74B527DD2856}"/>
   </bookViews>
